--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62492.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62492.xlsx
@@ -427,7 +427,11 @@
           <t>Module</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>1G</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -435,7 +439,11 @@
           <t>Professor</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DING</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -451,7 +459,11 @@
           <t>Code</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>81-01-61</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -527,7 +539,11 @@
           <t>Prénom</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Idrid</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -537,7 +553,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UJUBLUI</t>
+          <t>JAOUI</t>
         </is>
       </c>
     </row>
@@ -559,7 +575,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G00A</t>
+          <t>G78B</t>
         </is>
       </c>
     </row>
@@ -570,7 +586,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>62492</v>
       </c>
     </row>
     <row r="18">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62492.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62492.xlsx
@@ -451,7 +451,11 @@
           <t>Date</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -512,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -575,7 +579,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G78B</t>
+          <t>G78H</t>
         </is>
       </c>
     </row>
@@ -596,7 +600,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62492.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62492.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Idrid</t>
+          <t>Idris</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JAOUI</t>
+          <t>IAOVL</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +724,7 @@
         <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62492.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62492.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Idris</t>
+          <t>IDRIS</t>
         </is>
       </c>
     </row>
@@ -699,9 +699,6 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="J4" t="n">
-        <v>44</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62492.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62492.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
